--- a/コミッション報告_2026年10月/朴G/コミッション明細_2026年10月_朴G_まとめ.xlsx
+++ b/コミッション報告_2026年10月/朴G/コミッション明細_2026年10月_朴G_まとめ.xlsx
@@ -12,7 +12,7 @@
     <sheet name="明細" sheetId="2" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">明細!$A$3:$O$104</definedName>
+    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">明細!$A$3:$O$112</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="743" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="798" uniqueCount="150">
   <si>
     <r>
       <rPr>
@@ -161,6 +161,9 @@
   </si>
   <si>
     <t xml:space="preserve">Masuda, Mitsuru</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yon o Pak</t>
   </si>
   <si>
     <t xml:space="preserve">合計</t>
@@ -425,28 +428,6 @@
     <t xml:space="preserve">SPX20-X</t>
   </si>
   <si>
-    <t xml:space="preserve">EVO25</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">ライダー</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1</t>
-    </r>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="10"/>
@@ -500,6 +481,28 @@
     </r>
   </si>
   <si>
+    <t xml:space="preserve">EVO25</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ライダー</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">T20W044170</t>
   </si>
   <si>
@@ -848,6 +851,42 @@
   </si>
   <si>
     <t xml:space="preserve">Jihae Yang</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T15W081546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yudai Konishi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T20W044480</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taeil Lee</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T15W082100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kyohei Yamamoto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T15W082662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yuki Morioka</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T20W044625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kota Matsumoto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T15W065073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yuki Takaoka</t>
   </si>
 </sst>
 </file>
@@ -1338,7 +1377,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
@@ -1382,11 +1421,11 @@
         <v>7</v>
       </c>
       <c r="C4" s="4" t="n">
-        <f aca="false">COUNTIF(明細!$A$4:$A$104,A4)</f>
+        <f aca="false">COUNTIF(明細!$A$4:$A$112,A4)</f>
         <v>52</v>
       </c>
       <c r="D4" s="5" t="n">
-        <f aca="false">SUMIF(明細!$A$4:$A$104,A4,明細!$N$4:$N$104)</f>
+        <f aca="false">SUMIF(明細!$A$4:$A$112,A4,明細!$N$4:$N$112)</f>
         <v>23442</v>
       </c>
       <c r="E4" s="5" t="n">
@@ -1405,11 +1444,11 @@
         <v>8</v>
       </c>
       <c r="C5" s="4" t="n">
-        <f aca="false">COUNTIF(明細!$A$4:$A$104,A5)</f>
+        <f aca="false">COUNTIF(明細!$A$4:$A$112,A5)</f>
         <v>3</v>
       </c>
       <c r="D5" s="5" t="n">
-        <f aca="false">SUMIF(明細!$A$4:$A$104,A5,明細!$N$4:$N$104)</f>
+        <f aca="false">SUMIF(明細!$A$4:$A$112,A5,明細!$N$4:$N$112)</f>
         <v>1260</v>
       </c>
       <c r="E5" s="5" t="n">
@@ -1428,11 +1467,11 @@
         <v>9</v>
       </c>
       <c r="C6" s="4" t="n">
-        <f aca="false">COUNTIF(明細!$A$4:$A$104,A6)</f>
+        <f aca="false">COUNTIF(明細!$A$4:$A$112,A6)</f>
         <v>2</v>
       </c>
       <c r="D6" s="5" t="n">
-        <f aca="false">SUMIF(明細!$A$4:$A$104,A6,明細!$N$4:$N$104)</f>
+        <f aca="false">SUMIF(明細!$A$4:$A$112,A6,明細!$N$4:$N$112)</f>
         <v>960</v>
       </c>
       <c r="E6" s="5" t="n">
@@ -1451,11 +1490,11 @@
         <v>10</v>
       </c>
       <c r="C7" s="4" t="n">
-        <f aca="false">COUNTIF(明細!$A$4:$A$104,A7)</f>
+        <f aca="false">COUNTIF(明細!$A$4:$A$112,A7)</f>
         <v>1</v>
       </c>
       <c r="D7" s="5" t="n">
-        <f aca="false">SUMIF(明細!$A$4:$A$104,A7,明細!$N$4:$N$104)</f>
+        <f aca="false">SUMIF(明細!$A$4:$A$112,A7,明細!$N$4:$N$112)</f>
         <v>1260</v>
       </c>
       <c r="E7" s="5" t="n">
@@ -1474,11 +1513,11 @@
         <v>11</v>
       </c>
       <c r="C8" s="4" t="n">
-        <f aca="false">COUNTIF(明細!$A$4:$A$104,A8)</f>
+        <f aca="false">COUNTIF(明細!$A$4:$A$112,A8)</f>
         <v>2</v>
       </c>
       <c r="D8" s="5" t="n">
-        <f aca="false">SUMIF(明細!$A$4:$A$104,A8,明細!$N$4:$N$104)</f>
+        <f aca="false">SUMIF(明細!$A$4:$A$112,A8,明細!$N$4:$N$112)</f>
         <v>810</v>
       </c>
       <c r="E8" s="5" t="n">
@@ -1497,11 +1536,11 @@
         <v>12</v>
       </c>
       <c r="C9" s="4" t="n">
-        <f aca="false">COUNTIF(明細!$A$4:$A$104,A9)</f>
+        <f aca="false">COUNTIF(明細!$A$4:$A$112,A9)</f>
         <v>2</v>
       </c>
       <c r="D9" s="5" t="n">
-        <f aca="false">SUMIF(明細!$A$4:$A$104,A9,明細!$N$4:$N$104)</f>
+        <f aca="false">SUMIF(明細!$A$4:$A$112,A9,明細!$N$4:$N$112)</f>
         <v>4224</v>
       </c>
       <c r="E9" s="5" t="n">
@@ -1520,11 +1559,11 @@
         <v>13</v>
       </c>
       <c r="C10" s="4" t="n">
-        <f aca="false">COUNTIF(明細!$A$4:$A$104,A10)</f>
+        <f aca="false">COUNTIF(明細!$A$4:$A$112,A10)</f>
         <v>5</v>
       </c>
       <c r="D10" s="5" t="n">
-        <f aca="false">SUMIF(明細!$A$4:$A$104,A10,明細!$N$4:$N$104)</f>
+        <f aca="false">SUMIF(明細!$A$4:$A$112,A10,明細!$N$4:$N$112)</f>
         <v>2100</v>
       </c>
       <c r="E10" s="5" t="n">
@@ -1543,11 +1582,11 @@
         <v>14</v>
       </c>
       <c r="C11" s="4" t="n">
-        <f aca="false">COUNTIF(明細!$A$4:$A$104,A11)</f>
+        <f aca="false">COUNTIF(明細!$A$4:$A$112,A11)</f>
         <v>10</v>
       </c>
       <c r="D11" s="5" t="n">
-        <f aca="false">SUMIF(明細!$A$4:$A$104,A11,明細!$N$4:$N$104)</f>
+        <f aca="false">SUMIF(明細!$A$4:$A$112,A11,明細!$N$4:$N$112)</f>
         <v>3384</v>
       </c>
       <c r="E11" s="5" t="n">
@@ -1566,11 +1605,11 @@
         <v>15</v>
       </c>
       <c r="C12" s="4" t="n">
-        <f aca="false">COUNTIF(明細!$A$4:$A$104,A12)</f>
+        <f aca="false">COUNTIF(明細!$A$4:$A$112,A12)</f>
         <v>13</v>
       </c>
       <c r="D12" s="5" t="n">
-        <f aca="false">SUMIF(明細!$A$4:$A$104,A12,明細!$N$4:$N$104)</f>
+        <f aca="false">SUMIF(明細!$A$4:$A$112,A12,明細!$N$4:$N$112)</f>
         <v>16806</v>
       </c>
       <c r="E12" s="5" t="n">
@@ -1589,11 +1628,11 @@
         <v>16</v>
       </c>
       <c r="C13" s="4" t="n">
-        <f aca="false">COUNTIF(明細!$A$4:$A$104,A13)</f>
+        <f aca="false">COUNTIF(明細!$A$4:$A$112,A13)</f>
         <v>7</v>
       </c>
       <c r="D13" s="5" t="n">
-        <f aca="false">SUMIF(明細!$A$4:$A$104,A13,明細!$N$4:$N$104)</f>
+        <f aca="false">SUMIF(明細!$A$4:$A$112,A13,明細!$N$4:$N$112)</f>
         <v>1200</v>
       </c>
       <c r="E13" s="5" t="n">
@@ -1612,11 +1651,11 @@
         <v>17</v>
       </c>
       <c r="C14" s="4" t="n">
-        <f aca="false">COUNTIF(明細!$A$4:$A$104,A14)</f>
+        <f aca="false">COUNTIF(明細!$A$4:$A$112,A14)</f>
         <v>4</v>
       </c>
       <c r="D14" s="5" t="n">
-        <f aca="false">SUMIF(明細!$A$4:$A$104,A14,明細!$N$4:$N$104)</f>
+        <f aca="false">SUMIF(明細!$A$4:$A$112,A14,明細!$N$4:$N$112)</f>
         <v>1080</v>
       </c>
       <c r="E14" s="5" t="n">
@@ -1628,29 +1667,52 @@
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="6" t="s">
+      <c r="A15" s="4" t="n">
+        <v>1769</v>
+      </c>
+      <c r="B15" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C15" s="7" t="n">
-        <f aca="false">SUM(C4:C14)</f>
-        <v>101</v>
-      </c>
-      <c r="D15" s="8" t="n">
-        <f aca="false">SUM(D4:D14)</f>
-        <v>56526</v>
-      </c>
-      <c r="E15" s="8" t="n">
-        <f aca="false">SUM(E4:E14)</f>
-        <v>55</v>
-      </c>
-      <c r="F15" s="8" t="n">
-        <f aca="false">SUM(F4:F14)</f>
-        <v>56471</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="9" t="s">
+      <c r="C15" s="4" t="n">
+        <f aca="false">COUNTIF(明細!$A$4:$A$112,A15)</f>
+        <v>8</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <f aca="false">SUMIF(明細!$A$4:$A$112,A15,明細!$N$4:$N$112)</f>
+        <v>5297.25</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <f aca="false">IF(INT(D15)&lt;=E15,0,INT(D15)-E15)</f>
+        <v>5292</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B16" s="6" t="s">
         <v>19</v>
+      </c>
+      <c r="C16" s="7" t="n">
+        <f aca="false">SUM(C4:C15)</f>
+        <v>109</v>
+      </c>
+      <c r="D16" s="8" t="n">
+        <f aca="false">SUM(D4:D15)</f>
+        <v>61823.25</v>
+      </c>
+      <c r="E16" s="8" t="n">
+        <f aca="false">SUM(E4:E15)</f>
+        <v>60</v>
+      </c>
+      <c r="F16" s="8" t="n">
+        <f aca="false">SUM(F4:F15)</f>
+        <v>61763</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="9" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -1669,7 +1731,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:O104"/>
+  <dimension ref="A1:O112"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
@@ -1691,7 +1753,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1702,43 +1764,43 @@
         <v>2</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G3" s="10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H3" s="10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I3" s="10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J3" s="10" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K3" s="10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L3" s="10" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M3" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="N3" s="10" t="s">
         <v>6</v>
       </c>
       <c r="O3" s="10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1752,16 +1814,16 @@
         <v>1</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G4" s="12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H4" s="4" t="n">
         <v>1</v>
@@ -1776,7 +1838,7 @@
         <v>50</v>
       </c>
       <c r="L4" s="12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M4" s="4" t="n">
         <v>0</v>
@@ -1786,7 +1848,7 @@
         <v>0</v>
       </c>
       <c r="O4" s="15" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1800,16 +1862,16 @@
         <v>2</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G5" s="12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H5" s="4" t="n">
         <v>1</v>
@@ -1824,7 +1886,7 @@
         <v>50</v>
       </c>
       <c r="L5" s="12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M5" s="4" t="n">
         <v>0</v>
@@ -1834,7 +1896,7 @@
         <v>0</v>
       </c>
       <c r="O5" s="15" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1848,16 +1910,16 @@
         <v>3</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G6" s="12" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H6" s="4" t="n">
         <v>1</v>
@@ -1872,7 +1934,7 @@
         <v>37.5</v>
       </c>
       <c r="L6" s="12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M6" s="4" t="n">
         <v>0</v>
@@ -1882,7 +1944,7 @@
         <v>0</v>
       </c>
       <c r="O6" s="15" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1896,16 +1958,16 @@
         <v>4</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G7" s="12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H7" s="4" t="n">
         <v>1</v>
@@ -1920,7 +1982,7 @@
         <v>60</v>
       </c>
       <c r="L7" s="12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M7" s="4" t="n">
         <v>0</v>
@@ -1930,7 +1992,7 @@
         <v>0</v>
       </c>
       <c r="O7" s="15" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1944,16 +2006,16 @@
         <v>5</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G8" s="12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H8" s="4" t="n">
         <v>1</v>
@@ -1968,7 +2030,7 @@
         <v>100</v>
       </c>
       <c r="L8" s="12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M8" s="4" t="n">
         <v>0</v>
@@ -1978,7 +2040,7 @@
         <v>0</v>
       </c>
       <c r="O8" s="15" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1992,16 +2054,16 @@
         <v>6</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G9" s="12" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H9" s="4" t="n">
         <v>1</v>
@@ -2016,7 +2078,7 @@
         <v>45</v>
       </c>
       <c r="L9" s="12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M9" s="4" t="n">
         <v>12</v>
@@ -2026,7 +2088,7 @@
         <v>540</v>
       </c>
       <c r="O9" s="16" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2040,16 +2102,16 @@
         <v>7</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G10" s="12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H10" s="4" t="n">
         <v>1</v>
@@ -2064,7 +2126,7 @@
         <v>75</v>
       </c>
       <c r="L10" s="12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M10" s="4" t="n">
         <v>0</v>
@@ -2074,7 +2136,7 @@
         <v>0</v>
       </c>
       <c r="O10" s="15" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2088,16 +2150,16 @@
         <v>8</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G11" s="12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H11" s="4" t="n">
         <v>1</v>
@@ -2112,7 +2174,7 @@
         <v>50</v>
       </c>
       <c r="L11" s="12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M11" s="4" t="n">
         <v>0</v>
@@ -2122,7 +2184,7 @@
         <v>0</v>
       </c>
       <c r="O11" s="15" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2136,16 +2198,16 @@
         <v>9</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G12" s="12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H12" s="4" t="n">
         <v>1</v>
@@ -2160,7 +2222,7 @@
         <v>32</v>
       </c>
       <c r="L12" s="12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M12" s="4" t="n">
         <v>12</v>
@@ -2170,7 +2232,7 @@
         <v>384</v>
       </c>
       <c r="O12" s="16" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2184,16 +2246,16 @@
         <v>10</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G13" s="12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H13" s="4" t="n">
         <v>1</v>
@@ -2208,7 +2270,7 @@
         <v>25</v>
       </c>
       <c r="L13" s="12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M13" s="4" t="n">
         <v>0</v>
@@ -2218,7 +2280,7 @@
         <v>0</v>
       </c>
       <c r="O13" s="15" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2232,16 +2294,16 @@
         <v>11</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G14" s="12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H14" s="4" t="n">
         <v>1</v>
@@ -2256,7 +2318,7 @@
         <v>150</v>
       </c>
       <c r="L14" s="12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M14" s="4" t="n">
         <v>12</v>
@@ -2266,7 +2328,7 @@
         <v>1800</v>
       </c>
       <c r="O14" s="16" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2280,16 +2342,16 @@
         <v>12</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G15" s="12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H15" s="4" t="n">
         <v>1</v>
@@ -2304,7 +2366,7 @@
         <v>50</v>
       </c>
       <c r="L15" s="12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M15" s="4" t="n">
         <v>0</v>
@@ -2314,7 +2376,7 @@
         <v>0</v>
       </c>
       <c r="O15" s="15" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2328,16 +2390,16 @@
         <v>13</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G16" s="12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H16" s="4" t="n">
         <v>1</v>
@@ -2352,7 +2414,7 @@
         <v>75</v>
       </c>
       <c r="L16" s="12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M16" s="4" t="n">
         <v>0</v>
@@ -2362,7 +2424,7 @@
         <v>0</v>
       </c>
       <c r="O16" s="15" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2376,16 +2438,16 @@
         <v>14</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G17" s="12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H17" s="4" t="n">
         <v>1</v>
@@ -2400,7 +2462,7 @@
         <v>20</v>
       </c>
       <c r="L17" s="12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M17" s="4" t="n">
         <v>0</v>
@@ -2410,7 +2472,7 @@
         <v>0</v>
       </c>
       <c r="O17" s="15" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2424,16 +2486,16 @@
         <v>15</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G18" s="12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H18" s="4" t="n">
         <v>1</v>
@@ -2448,7 +2510,7 @@
         <v>66.25</v>
       </c>
       <c r="L18" s="12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M18" s="4" t="n">
         <v>12</v>
@@ -2458,7 +2520,7 @@
         <v>795</v>
       </c>
       <c r="O18" s="16" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2472,16 +2534,16 @@
         <v>16</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G19" s="12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H19" s="4" t="n">
         <v>1</v>
@@ -2496,7 +2558,7 @@
         <v>37.5</v>
       </c>
       <c r="L19" s="12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M19" s="4" t="n">
         <v>0</v>
@@ -2506,7 +2568,7 @@
         <v>0</v>
       </c>
       <c r="O19" s="15" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2520,16 +2582,16 @@
         <v>17</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G20" s="12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H20" s="4" t="n">
         <v>1</v>
@@ -2544,7 +2606,7 @@
         <v>60</v>
       </c>
       <c r="L20" s="12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M20" s="4" t="n">
         <v>12</v>
@@ -2554,7 +2616,7 @@
         <v>720</v>
       </c>
       <c r="O20" s="16" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2568,16 +2630,16 @@
         <v>18</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G21" s="12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H21" s="4" t="n">
         <v>1</v>
@@ -2592,7 +2654,7 @@
         <v>45</v>
       </c>
       <c r="L21" s="12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M21" s="4" t="n">
         <v>12</v>
@@ -2602,7 +2664,7 @@
         <v>540</v>
       </c>
       <c r="O21" s="16" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2616,16 +2678,16 @@
         <v>19</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G22" s="12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H22" s="4" t="n">
         <v>1</v>
@@ -2640,7 +2702,7 @@
         <v>25</v>
       </c>
       <c r="L22" s="12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M22" s="4" t="n">
         <v>0</v>
@@ -2650,7 +2712,7 @@
         <v>0</v>
       </c>
       <c r="O22" s="15" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2664,16 +2726,16 @@
         <v>20</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G23" s="12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H23" s="4" t="n">
         <v>1</v>
@@ -2688,7 +2750,7 @@
         <v>90</v>
       </c>
       <c r="L23" s="12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M23" s="4" t="n">
         <v>12</v>
@@ -2698,7 +2760,7 @@
         <v>1080</v>
       </c>
       <c r="O23" s="16" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2712,16 +2774,16 @@
         <v>21</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G24" s="12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H24" s="4" t="n">
         <v>1</v>
@@ -2736,7 +2798,7 @@
         <v>90</v>
       </c>
       <c r="L24" s="12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M24" s="4" t="n">
         <v>12</v>
@@ -2746,7 +2808,7 @@
         <v>1080</v>
       </c>
       <c r="O24" s="16" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2760,16 +2822,16 @@
         <v>22</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G25" s="12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H25" s="4" t="n">
         <v>1</v>
@@ -2784,7 +2846,7 @@
         <v>90</v>
       </c>
       <c r="L25" s="12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M25" s="4" t="n">
         <v>0</v>
@@ -2794,7 +2856,7 @@
         <v>0</v>
       </c>
       <c r="O25" s="15" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2808,16 +2870,16 @@
         <v>23</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G26" s="12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H26" s="4" t="n">
         <v>1</v>
@@ -2832,7 +2894,7 @@
         <v>225</v>
       </c>
       <c r="L26" s="12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M26" s="4" t="n">
         <v>12</v>
@@ -2842,7 +2904,7 @@
         <v>2700</v>
       </c>
       <c r="O26" s="16" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2856,16 +2918,16 @@
         <v>24</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G27" s="12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H27" s="4" t="n">
         <v>1</v>
@@ -2880,7 +2942,7 @@
         <v>50</v>
       </c>
       <c r="L27" s="12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M27" s="4" t="n">
         <v>0</v>
@@ -2890,7 +2952,7 @@
         <v>0</v>
       </c>
       <c r="O27" s="15" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2904,16 +2966,16 @@
         <v>25</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G28" s="12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H28" s="4" t="n">
         <v>1</v>
@@ -2928,7 +2990,7 @@
         <v>66.25</v>
       </c>
       <c r="L28" s="12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M28" s="4" t="n">
         <v>12</v>
@@ -2938,7 +3000,7 @@
         <v>795</v>
       </c>
       <c r="O28" s="16" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2952,16 +3014,16 @@
         <v>26</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G29" s="12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H29" s="4" t="n">
         <v>1</v>
@@ -2976,7 +3038,7 @@
         <v>50</v>
       </c>
       <c r="L29" s="12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M29" s="4" t="n">
         <v>0</v>
@@ -2986,7 +3048,7 @@
         <v>0</v>
       </c>
       <c r="O29" s="15" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3000,16 +3062,16 @@
         <v>27</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G30" s="12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H30" s="4" t="n">
         <v>1</v>
@@ -3024,7 +3086,7 @@
         <v>20</v>
       </c>
       <c r="L30" s="12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M30" s="4" t="n">
         <v>0</v>
@@ -3034,7 +3096,7 @@
         <v>0</v>
       </c>
       <c r="O30" s="15" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3048,16 +3110,16 @@
         <v>28</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G31" s="12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H31" s="4" t="n">
         <v>1</v>
@@ -3072,7 +3134,7 @@
         <v>120</v>
       </c>
       <c r="L31" s="12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M31" s="4" t="n">
         <v>0</v>
@@ -3082,7 +3144,7 @@
         <v>0</v>
       </c>
       <c r="O31" s="15" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3096,16 +3158,16 @@
         <v>29</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G32" s="12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H32" s="4" t="n">
         <v>1</v>
@@ -3120,7 +3182,7 @@
         <v>75</v>
       </c>
       <c r="L32" s="12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M32" s="4" t="n">
         <v>0</v>
@@ -3130,7 +3192,7 @@
         <v>0</v>
       </c>
       <c r="O32" s="15" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3144,16 +3206,16 @@
         <v>30</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G33" s="12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H33" s="4" t="n">
         <v>1</v>
@@ -3168,7 +3230,7 @@
         <v>90</v>
       </c>
       <c r="L33" s="12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M33" s="4" t="n">
         <v>0</v>
@@ -3178,7 +3240,7 @@
         <v>0</v>
       </c>
       <c r="O33" s="15" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3192,16 +3254,16 @@
         <v>31</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G34" s="12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H34" s="4" t="n">
         <v>1</v>
@@ -3216,7 +3278,7 @@
         <v>50</v>
       </c>
       <c r="L34" s="12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M34" s="4" t="n">
         <v>0</v>
@@ -3226,7 +3288,7 @@
         <v>0</v>
       </c>
       <c r="O34" s="15" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3240,16 +3302,16 @@
         <v>32</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G35" s="12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H35" s="4" t="n">
         <v>1</v>
@@ -3264,7 +3326,7 @@
         <v>32</v>
       </c>
       <c r="L35" s="12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M35" s="4" t="n">
         <v>12</v>
@@ -3274,7 +3336,7 @@
         <v>384</v>
       </c>
       <c r="O35" s="16" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3288,16 +3350,16 @@
         <v>33</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G36" s="12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H36" s="4" t="n">
         <v>1</v>
@@ -3312,7 +3374,7 @@
         <v>66.25</v>
       </c>
       <c r="L36" s="12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M36" s="4" t="n">
         <v>0</v>
@@ -3322,7 +3384,7 @@
         <v>0</v>
       </c>
       <c r="O36" s="15" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3336,16 +3398,16 @@
         <v>34</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G37" s="12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H37" s="4" t="n">
         <v>1</v>
@@ -3360,7 +3422,7 @@
         <v>50</v>
       </c>
       <c r="L37" s="12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M37" s="4" t="n">
         <v>0</v>
@@ -3370,7 +3432,7 @@
         <v>0</v>
       </c>
       <c r="O37" s="15" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3384,16 +3446,16 @@
         <v>35</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G38" s="12" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H38" s="4" t="n">
         <v>1</v>
@@ -3408,7 +3470,7 @@
         <v>25</v>
       </c>
       <c r="L38" s="12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M38" s="4" t="n">
         <v>0</v>
@@ -3418,7 +3480,7 @@
         <v>0</v>
       </c>
       <c r="O38" s="15" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3432,16 +3494,16 @@
         <v>36</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G39" s="12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H39" s="4" t="n">
         <v>1</v>
@@ -3456,7 +3518,7 @@
         <v>60</v>
       </c>
       <c r="L39" s="12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M39" s="4" t="n">
         <v>0</v>
@@ -3466,7 +3528,7 @@
         <v>0</v>
       </c>
       <c r="O39" s="15" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3480,16 +3542,16 @@
         <v>37</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G40" s="12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H40" s="4" t="n">
         <v>1</v>
@@ -3504,7 +3566,7 @@
         <v>50</v>
       </c>
       <c r="L40" s="12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M40" s="4" t="n">
         <v>0</v>
@@ -3514,7 +3576,7 @@
         <v>0</v>
       </c>
       <c r="O40" s="15" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3528,16 +3590,16 @@
         <v>38</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G41" s="12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H41" s="4" t="n">
         <v>1</v>
@@ -3552,7 +3614,7 @@
         <v>50</v>
       </c>
       <c r="L41" s="12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M41" s="4" t="n">
         <v>0</v>
@@ -3562,7 +3624,7 @@
         <v>0</v>
       </c>
       <c r="O41" s="15" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3576,16 +3638,16 @@
         <v>39</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G42" s="12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H42" s="4" t="n">
         <v>1</v>
@@ -3600,7 +3662,7 @@
         <v>37.5</v>
       </c>
       <c r="L42" s="12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M42" s="4" t="n">
         <v>0</v>
@@ -3610,7 +3672,7 @@
         <v>0</v>
       </c>
       <c r="O42" s="15" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3624,16 +3686,16 @@
         <v>40</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G43" s="12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H43" s="4" t="n">
         <v>1</v>
@@ -3648,7 +3710,7 @@
         <v>81</v>
       </c>
       <c r="L43" s="12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M43" s="4" t="n">
         <v>12</v>
@@ -3658,7 +3720,7 @@
         <v>972</v>
       </c>
       <c r="O43" s="16" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3672,16 +3734,16 @@
         <v>41</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G44" s="12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H44" s="4" t="n">
         <v>1</v>
@@ -3696,7 +3758,7 @@
         <v>80</v>
       </c>
       <c r="L44" s="12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M44" s="4" t="n">
         <v>0</v>
@@ -3706,7 +3768,7 @@
         <v>0</v>
       </c>
       <c r="O44" s="15" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3720,16 +3782,16 @@
         <v>42</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G45" s="12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H45" s="4" t="n">
         <v>1</v>
@@ -3744,7 +3806,7 @@
         <v>50</v>
       </c>
       <c r="L45" s="12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M45" s="4" t="n">
         <v>0</v>
@@ -3754,7 +3816,7 @@
         <v>0</v>
       </c>
       <c r="O45" s="15" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3768,16 +3830,16 @@
         <v>43</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G46" s="12" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H46" s="4" t="n">
         <v>1</v>
@@ -3792,7 +3854,7 @@
         <v>15</v>
       </c>
       <c r="L46" s="12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M46" s="4" t="n">
         <v>12</v>
@@ -3802,7 +3864,7 @@
         <v>180</v>
       </c>
       <c r="O46" s="16" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3816,16 +3878,16 @@
         <v>44</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G47" s="12" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H47" s="4" t="n">
         <v>1</v>
@@ -3840,7 +3902,7 @@
         <v>525</v>
       </c>
       <c r="L47" s="12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M47" s="4" t="n">
         <v>12</v>
@@ -3850,7 +3912,7 @@
         <v>6300</v>
       </c>
       <c r="O47" s="16" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3864,16 +3926,16 @@
         <v>45</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G48" s="12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H48" s="4" t="n">
         <v>1</v>
@@ -3888,7 +3950,7 @@
         <v>120</v>
       </c>
       <c r="L48" s="12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M48" s="4" t="n">
         <v>12</v>
@@ -3898,7 +3960,7 @@
         <v>1440</v>
       </c>
       <c r="O48" s="16" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3912,16 +3974,16 @@
         <v>46</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G49" s="12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H49" s="4" t="n">
         <v>1</v>
@@ -3936,7 +3998,7 @@
         <v>50</v>
       </c>
       <c r="L49" s="12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M49" s="4" t="n">
         <v>0</v>
@@ -3946,7 +4008,7 @@
         <v>0</v>
       </c>
       <c r="O49" s="15" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3960,16 +4022,16 @@
         <v>47</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G50" s="12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H50" s="4" t="n">
         <v>1</v>
@@ -3984,7 +4046,7 @@
         <v>96</v>
       </c>
       <c r="L50" s="12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M50" s="4" t="n">
         <v>12</v>
@@ -3994,7 +4056,7 @@
         <v>1152</v>
       </c>
       <c r="O50" s="16" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4008,16 +4070,16 @@
         <v>48</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G51" s="12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H51" s="4" t="n">
         <v>1</v>
@@ -4032,7 +4094,7 @@
         <v>50</v>
       </c>
       <c r="L51" s="12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M51" s="4" t="n">
         <v>0</v>
@@ -4042,7 +4104,7 @@
         <v>0</v>
       </c>
       <c r="O51" s="15" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4056,16 +4118,16 @@
         <v>49</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G52" s="12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H52" s="4" t="n">
         <v>1</v>
@@ -4080,7 +4142,7 @@
         <v>90</v>
       </c>
       <c r="L52" s="12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M52" s="4" t="n">
         <v>12</v>
@@ -4090,7 +4152,7 @@
         <v>1080</v>
       </c>
       <c r="O52" s="16" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4104,16 +4166,16 @@
         <v>50</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G53" s="12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H53" s="4" t="n">
         <v>1</v>
@@ -4128,7 +4190,7 @@
         <v>40</v>
       </c>
       <c r="L53" s="12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M53" s="4" t="n">
         <v>0</v>
@@ -4138,7 +4200,7 @@
         <v>0</v>
       </c>
       <c r="O53" s="15" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4152,16 +4214,16 @@
         <v>51</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G54" s="12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H54" s="4" t="n">
         <v>1</v>
@@ -4176,7 +4238,7 @@
         <v>50</v>
       </c>
       <c r="L54" s="12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M54" s="4" t="n">
         <v>12</v>
@@ -4186,7 +4248,7 @@
         <v>600</v>
       </c>
       <c r="O54" s="16" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4200,16 +4262,16 @@
         <v>52</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G55" s="12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H55" s="4" t="n">
         <v>1</v>
@@ -4224,7 +4286,7 @@
         <v>75</v>
       </c>
       <c r="L55" s="12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M55" s="4" t="n">
         <v>12</v>
@@ -4234,7 +4296,7 @@
         <v>900</v>
       </c>
       <c r="O55" s="16" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4248,16 +4310,16 @@
         <v>53</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G56" s="12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H56" s="4" t="n">
         <v>1</v>
@@ -4272,7 +4334,7 @@
         <v>105</v>
       </c>
       <c r="L56" s="12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M56" s="4" t="n">
         <v>12</v>
@@ -4282,7 +4344,7 @@
         <v>1260</v>
       </c>
       <c r="O56" s="16" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4296,16 +4358,16 @@
         <v>54</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G57" s="12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H57" s="4" t="n">
         <v>1</v>
@@ -4320,7 +4382,7 @@
         <v>70</v>
       </c>
       <c r="L57" s="12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M57" s="4" t="n">
         <v>0</v>
@@ -4330,7 +4392,7 @@
         <v>0</v>
       </c>
       <c r="O57" s="15" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4344,16 +4406,16 @@
         <v>55</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G58" s="12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H58" s="4" t="n">
         <v>1</v>
@@ -4368,7 +4430,7 @@
         <v>70</v>
       </c>
       <c r="L58" s="12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M58" s="4" t="n">
         <v>0</v>
@@ -4378,7 +4440,7 @@
         <v>0</v>
       </c>
       <c r="O58" s="15" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4392,16 +4454,16 @@
         <v>56</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G59" s="12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H59" s="4" t="n">
         <v>1</v>
@@ -4416,7 +4478,7 @@
         <v>40</v>
       </c>
       <c r="L59" s="12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M59" s="4" t="n">
         <v>0</v>
@@ -4426,7 +4488,7 @@
         <v>0</v>
       </c>
       <c r="O59" s="15" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4440,16 +4502,16 @@
         <v>57</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E60" s="4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G60" s="12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H60" s="4" t="n">
         <v>1</v>
@@ -4464,7 +4526,7 @@
         <v>80</v>
       </c>
       <c r="L60" s="12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M60" s="4" t="n">
         <v>12</v>
@@ -4474,7 +4536,7 @@
         <v>960</v>
       </c>
       <c r="O60" s="16" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4488,16 +4550,16 @@
         <v>58</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G61" s="12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H61" s="4" t="n">
         <v>1</v>
@@ -4512,7 +4574,7 @@
         <v>105</v>
       </c>
       <c r="L61" s="12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M61" s="4" t="n">
         <v>12</v>
@@ -4522,7 +4584,7 @@
         <v>1260</v>
       </c>
       <c r="O61" s="16" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4536,16 +4598,16 @@
         <v>59</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E62" s="4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G62" s="12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H62" s="4" t="n">
         <v>1</v>
@@ -4560,7 +4622,7 @@
         <v>50</v>
       </c>
       <c r="L62" s="12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M62" s="4" t="n">
         <v>12</v>
@@ -4570,7 +4632,7 @@
         <v>600</v>
       </c>
       <c r="O62" s="16" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4584,16 +4646,16 @@
         <v>60</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G63" s="12" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H63" s="4" t="n">
         <v>1</v>
@@ -4608,7 +4670,7 @@
         <v>17.5</v>
       </c>
       <c r="L63" s="12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M63" s="4" t="n">
         <v>12</v>
@@ -4618,7 +4680,7 @@
         <v>210</v>
       </c>
       <c r="O63" s="16" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4632,16 +4694,16 @@
         <v>61</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G64" s="12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H64" s="4" t="n">
         <v>1</v>
@@ -4656,7 +4718,7 @@
         <v>176</v>
       </c>
       <c r="L64" s="12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M64" s="4" t="n">
         <v>12</v>
@@ -4666,7 +4728,7 @@
         <v>2112</v>
       </c>
       <c r="O64" s="16" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4680,16 +4742,16 @@
         <v>62</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G65" s="12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H65" s="4" t="n">
         <v>1</v>
@@ -4704,7 +4766,7 @@
         <v>176</v>
       </c>
       <c r="L65" s="12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M65" s="4" t="n">
         <v>12</v>
@@ -4714,7 +4776,7 @@
         <v>2112</v>
       </c>
       <c r="O65" s="16" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4728,16 +4790,16 @@
         <v>63</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G66" s="12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H66" s="4" t="n">
         <v>1</v>
@@ -4752,7 +4814,7 @@
         <v>60</v>
       </c>
       <c r="L66" s="12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M66" s="4" t="n">
         <v>0</v>
@@ -4762,7 +4824,7 @@
         <v>0</v>
       </c>
       <c r="O66" s="15" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4776,16 +4838,16 @@
         <v>64</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E67" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G67" s="12" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H67" s="4" t="n">
         <v>1</v>
@@ -4800,7 +4862,7 @@
         <v>52.5</v>
       </c>
       <c r="L67" s="12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M67" s="4" t="n">
         <v>0</v>
@@ -4810,7 +4872,7 @@
         <v>0</v>
       </c>
       <c r="O67" s="15" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4824,16 +4886,16 @@
         <v>65</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E68" s="4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G68" s="12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H68" s="4" t="n">
         <v>1</v>
@@ -4848,7 +4910,7 @@
         <v>175</v>
       </c>
       <c r="L68" s="12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M68" s="4" t="n">
         <v>12</v>
@@ -4858,7 +4920,7 @@
         <v>2100</v>
       </c>
       <c r="O68" s="16" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4872,16 +4934,16 @@
         <v>66</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G69" s="12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H69" s="4" t="n">
         <v>1</v>
@@ -4896,7 +4958,7 @@
         <v>35</v>
       </c>
       <c r="L69" s="12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M69" s="4" t="n">
         <v>0</v>
@@ -4906,7 +4968,7 @@
         <v>0</v>
       </c>
       <c r="O69" s="15" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4920,16 +4982,16 @@
         <v>67</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E70" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F70" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G70" s="12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H70" s="4" t="n">
         <v>1</v>
@@ -4944,7 +5006,7 @@
         <v>60</v>
       </c>
       <c r="L70" s="12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M70" s="4" t="n">
         <v>0</v>
@@ -4954,7 +5016,7 @@
         <v>0</v>
       </c>
       <c r="O70" s="15" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4968,16 +5030,16 @@
         <v>68</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E71" s="4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G71" s="12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H71" s="4" t="n">
         <v>1</v>
@@ -4992,7 +5054,7 @@
         <v>100</v>
       </c>
       <c r="L71" s="12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M71" s="4" t="n">
         <v>0</v>
@@ -5002,7 +5064,7 @@
         <v>0</v>
       </c>
       <c r="O71" s="15" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5016,16 +5078,16 @@
         <v>69</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E72" s="4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F72" s="4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G72" s="12" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H72" s="4" t="n">
         <v>1</v>
@@ -5040,7 +5102,7 @@
         <v>52.5</v>
       </c>
       <c r="L72" s="12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M72" s="4" t="n">
         <v>12</v>
@@ -5050,7 +5112,7 @@
         <v>630</v>
       </c>
       <c r="O72" s="16" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5064,16 +5126,16 @@
         <v>70</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E73" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F73" s="4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G73" s="12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H73" s="4" t="n">
         <v>1</v>
@@ -5088,7 +5150,7 @@
         <v>35</v>
       </c>
       <c r="L73" s="12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M73" s="4" t="n">
         <v>0</v>
@@ -5098,7 +5160,7 @@
         <v>0</v>
       </c>
       <c r="O73" s="15" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5112,16 +5174,16 @@
         <v>71</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E74" s="4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F74" s="4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G74" s="12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H74" s="4" t="n">
         <v>1</v>
@@ -5136,7 +5198,7 @@
         <v>105</v>
       </c>
       <c r="L74" s="12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M74" s="4" t="n">
         <v>0</v>
@@ -5146,7 +5208,7 @@
         <v>0</v>
       </c>
       <c r="O74" s="15" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5160,16 +5222,16 @@
         <v>72</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E75" s="4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F75" s="4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G75" s="12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H75" s="4" t="n">
         <v>1</v>
@@ -5184,7 +5246,7 @@
         <v>52.5</v>
       </c>
       <c r="L75" s="12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M75" s="4" t="n">
         <v>12</v>
@@ -5194,7 +5256,7 @@
         <v>630</v>
       </c>
       <c r="O75" s="16" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5208,16 +5270,16 @@
         <v>73</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E76" s="4" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F76" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G76" s="12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H76" s="4" t="n">
         <v>1</v>
@@ -5232,7 +5294,7 @@
         <v>79.5</v>
       </c>
       <c r="L76" s="12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M76" s="4" t="n">
         <v>0</v>
@@ -5242,7 +5304,7 @@
         <v>0</v>
       </c>
       <c r="O76" s="15" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5256,16 +5318,16 @@
         <v>74</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E77" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F77" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G77" s="12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H77" s="4" t="n">
         <v>1</v>
@@ -5280,7 +5342,7 @@
         <v>60</v>
       </c>
       <c r="L77" s="12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M77" s="4" t="n">
         <v>0</v>
@@ -5290,7 +5352,7 @@
         <v>0</v>
       </c>
       <c r="O77" s="15" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5304,16 +5366,16 @@
         <v>75</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E78" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F78" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G78" s="12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H78" s="4" t="n">
         <v>1</v>
@@ -5328,7 +5390,7 @@
         <v>81</v>
       </c>
       <c r="L78" s="12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M78" s="4" t="n">
         <v>12</v>
@@ -5338,7 +5400,7 @@
         <v>972</v>
       </c>
       <c r="O78" s="16" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5352,16 +5414,16 @@
         <v>76</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E79" s="4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F79" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G79" s="12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H79" s="4" t="n">
         <v>1</v>
@@ -5376,7 +5438,7 @@
         <v>96</v>
       </c>
       <c r="L79" s="12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M79" s="4" t="n">
         <v>12</v>
@@ -5386,7 +5448,7 @@
         <v>1152</v>
       </c>
       <c r="O79" s="16" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5400,16 +5462,16 @@
         <v>77</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E80" s="4" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F80" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G80" s="12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H80" s="4" t="n">
         <v>1</v>
@@ -5424,7 +5486,7 @@
         <v>50</v>
       </c>
       <c r="L80" s="12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M80" s="4" t="n">
         <v>0</v>
@@ -5434,7 +5496,7 @@
         <v>0</v>
       </c>
       <c r="O80" s="15" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5448,16 +5510,16 @@
         <v>78</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E81" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F81" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G81" s="12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H81" s="4" t="n">
         <v>1</v>
@@ -5472,7 +5534,7 @@
         <v>105</v>
       </c>
       <c r="L81" s="12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M81" s="4" t="n">
         <v>0</v>
@@ -5482,7 +5544,7 @@
         <v>0</v>
       </c>
       <c r="O81" s="15" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5496,16 +5558,16 @@
         <v>79</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E82" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F82" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G82" s="12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H82" s="4" t="n">
         <v>1</v>
@@ -5520,7 +5582,7 @@
         <v>92.75</v>
       </c>
       <c r="L82" s="12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M82" s="4" t="n">
         <v>12</v>
@@ -5530,7 +5592,7 @@
         <v>1113</v>
       </c>
       <c r="O82" s="16" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5544,16 +5606,16 @@
         <v>80</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E83" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F83" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G83" s="12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H83" s="4" t="n">
         <v>1</v>
@@ -5568,7 +5630,7 @@
         <v>135</v>
       </c>
       <c r="L83" s="12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M83" s="4" t="n">
         <v>0</v>
@@ -5578,7 +5640,7 @@
         <v>0</v>
       </c>
       <c r="O83" s="15" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5592,16 +5654,16 @@
         <v>81</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E84" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F84" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G84" s="12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H84" s="4" t="n">
         <v>1</v>
@@ -5616,7 +5678,7 @@
         <v>270</v>
       </c>
       <c r="L84" s="12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M84" s="4" t="n">
         <v>12</v>
@@ -5626,7 +5688,7 @@
         <v>3240</v>
       </c>
       <c r="O84" s="16" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5640,16 +5702,16 @@
         <v>82</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E85" s="4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F85" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G85" s="12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H85" s="4" t="n">
         <v>1</v>
@@ -5664,7 +5726,7 @@
         <v>92.75</v>
       </c>
       <c r="L85" s="12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M85" s="4" t="n">
         <v>12</v>
@@ -5674,7 +5736,7 @@
         <v>1113</v>
       </c>
       <c r="O85" s="16" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5688,16 +5750,16 @@
         <v>83</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E86" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F86" s="4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G86" s="12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H86" s="4" t="n">
         <v>1</v>
@@ -5712,7 +5774,7 @@
         <v>40</v>
       </c>
       <c r="L86" s="12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M86" s="4" t="n">
         <v>0</v>
@@ -5722,7 +5784,7 @@
         <v>0</v>
       </c>
       <c r="O86" s="15" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5736,16 +5798,16 @@
         <v>84</v>
       </c>
       <c r="D87" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E87" s="4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F87" s="4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G87" s="12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H87" s="4" t="n">
         <v>1</v>
@@ -5760,7 +5822,7 @@
         <v>240</v>
       </c>
       <c r="L87" s="12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M87" s="4" t="n">
         <v>0</v>
@@ -5770,7 +5832,7 @@
         <v>0</v>
       </c>
       <c r="O87" s="15" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5784,16 +5846,16 @@
         <v>85</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E88" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F88" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G88" s="12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H88" s="4" t="n">
         <v>1</v>
@@ -5808,7 +5870,7 @@
         <v>157.5</v>
       </c>
       <c r="L88" s="12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M88" s="4" t="n">
         <v>0</v>
@@ -5818,7 +5880,7 @@
         <v>0</v>
       </c>
       <c r="O88" s="15" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5832,16 +5894,16 @@
         <v>86</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E89" s="4" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F89" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G89" s="12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H89" s="4" t="n">
         <v>1</v>
@@ -5856,7 +5918,7 @@
         <v>90</v>
       </c>
       <c r="L89" s="12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M89" s="4" t="n">
         <v>0</v>
@@ -5866,7 +5928,7 @@
         <v>0</v>
       </c>
       <c r="O89" s="15" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5880,16 +5942,16 @@
         <v>87</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E90" s="4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F90" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G90" s="12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H90" s="4" t="n">
         <v>1</v>
@@ -5904,7 +5966,7 @@
         <v>120</v>
       </c>
       <c r="L90" s="12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M90" s="4" t="n">
         <v>0</v>
@@ -5914,7 +5976,7 @@
         <v>0</v>
       </c>
       <c r="O90" s="15" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5928,16 +5990,16 @@
         <v>88</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E91" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F91" s="4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G91" s="12" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H91" s="4" t="n">
         <v>1</v>
@@ -5952,7 +6014,7 @@
         <v>840</v>
       </c>
       <c r="L91" s="12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M91" s="4" t="n">
         <v>12</v>
@@ -5962,7 +6024,7 @@
         <v>10080</v>
       </c>
       <c r="O91" s="16" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5976,16 +6038,16 @@
         <v>89</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E92" s="4" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F92" s="4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G92" s="12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H92" s="4" t="n">
         <v>1</v>
@@ -6000,7 +6062,7 @@
         <v>80</v>
       </c>
       <c r="L92" s="12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M92" s="4" t="n">
         <v>0</v>
@@ -6010,7 +6072,7 @@
         <v>0</v>
       </c>
       <c r="O92" s="15" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6024,16 +6086,16 @@
         <v>90</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E93" s="4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F93" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G93" s="12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H93" s="4" t="n">
         <v>1</v>
@@ -6048,7 +6110,7 @@
         <v>105</v>
       </c>
       <c r="L93" s="12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M93" s="4" t="n">
         <v>12</v>
@@ -6058,7 +6120,7 @@
         <v>1260</v>
       </c>
       <c r="O93" s="16" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6072,16 +6134,16 @@
         <v>91</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E94" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F94" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G94" s="12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H94" s="4" t="n">
         <v>1</v>
@@ -6096,7 +6158,7 @@
         <v>50</v>
       </c>
       <c r="L94" s="12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M94" s="4" t="n">
         <v>0</v>
@@ -6106,7 +6168,7 @@
         <v>0</v>
       </c>
       <c r="O94" s="15" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6120,16 +6182,16 @@
         <v>92</v>
       </c>
       <c r="D95" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E95" s="4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F95" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G95" s="12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H95" s="4" t="n">
         <v>1</v>
@@ -6144,7 +6206,7 @@
         <v>50</v>
       </c>
       <c r="L95" s="12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M95" s="4" t="n">
         <v>0</v>
@@ -6154,7 +6216,7 @@
         <v>0</v>
       </c>
       <c r="O95" s="15" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6168,16 +6230,16 @@
         <v>93</v>
       </c>
       <c r="D96" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E96" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F96" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G96" s="12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H96" s="4" t="n">
         <v>1</v>
@@ -6192,7 +6254,7 @@
         <v>75</v>
       </c>
       <c r="L96" s="12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M96" s="4" t="n">
         <v>0</v>
@@ -6202,7 +6264,7 @@
         <v>0</v>
       </c>
       <c r="O96" s="15" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6216,16 +6278,16 @@
         <v>94</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E97" s="4" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F97" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G97" s="12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H97" s="4" t="n">
         <v>1</v>
@@ -6240,7 +6302,7 @@
         <v>50</v>
       </c>
       <c r="L97" s="12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M97" s="4" t="n">
         <v>0</v>
@@ -6250,7 +6312,7 @@
         <v>0</v>
       </c>
       <c r="O97" s="15" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6264,16 +6326,16 @@
         <v>95</v>
       </c>
       <c r="D98" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E98" s="4" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F98" s="4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G98" s="12" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H98" s="4" t="n">
         <v>1</v>
@@ -6288,7 +6350,7 @@
         <v>35</v>
       </c>
       <c r="L98" s="12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M98" s="4" t="n">
         <v>0</v>
@@ -6298,7 +6360,7 @@
         <v>0</v>
       </c>
       <c r="O98" s="15" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6312,16 +6374,16 @@
         <v>96</v>
       </c>
       <c r="D99" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E99" s="4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F99" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G99" s="12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H99" s="4" t="n">
         <v>1</v>
@@ -6336,7 +6398,7 @@
         <v>50</v>
       </c>
       <c r="L99" s="12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M99" s="4" t="n">
         <v>0</v>
@@ -6346,7 +6408,7 @@
         <v>0</v>
       </c>
       <c r="O99" s="15" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6360,16 +6422,16 @@
         <v>97</v>
       </c>
       <c r="D100" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E100" s="4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F100" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G100" s="12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H100" s="4" t="n">
         <v>1</v>
@@ -6384,7 +6446,7 @@
         <v>100</v>
       </c>
       <c r="L100" s="12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M100" s="4" t="n">
         <v>12</v>
@@ -6394,7 +6456,7 @@
         <v>1200</v>
       </c>
       <c r="O100" s="16" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6408,16 +6470,16 @@
         <v>98</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E101" s="4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F101" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G101" s="12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H101" s="4" t="n">
         <v>1</v>
@@ -6432,7 +6494,7 @@
         <v>90</v>
       </c>
       <c r="L101" s="12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M101" s="4" t="n">
         <v>0</v>
@@ -6442,7 +6504,7 @@
         <v>0</v>
       </c>
       <c r="O101" s="15" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6456,16 +6518,16 @@
         <v>99</v>
       </c>
       <c r="D102" s="4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E102" s="4" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F102" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G102" s="12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H102" s="4" t="n">
         <v>1</v>
@@ -6480,7 +6542,7 @@
         <v>60</v>
       </c>
       <c r="L102" s="12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M102" s="4" t="n">
         <v>0</v>
@@ -6490,7 +6552,7 @@
         <v>0</v>
       </c>
       <c r="O102" s="15" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6504,16 +6566,16 @@
         <v>100</v>
       </c>
       <c r="D103" s="4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E103" s="4" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F103" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G103" s="12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H103" s="4" t="n">
         <v>1</v>
@@ -6528,7 +6590,7 @@
         <v>60</v>
       </c>
       <c r="L103" s="12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M103" s="4" t="n">
         <v>0</v>
@@ -6538,7 +6600,7 @@
         <v>0</v>
       </c>
       <c r="O103" s="15" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6552,16 +6614,16 @@
         <v>101</v>
       </c>
       <c r="D104" s="4" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E104" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F104" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G104" s="12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H104" s="4" t="n">
         <v>1</v>
@@ -6576,7 +6638,7 @@
         <v>90</v>
       </c>
       <c r="L104" s="12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M104" s="4" t="n">
         <v>12</v>
@@ -6586,11 +6648,391 @@
         <v>1080</v>
       </c>
       <c r="O104" s="16" t="s">
-        <v>49</v>
-      </c>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A105" s="4" t="n">
+        <v>1769</v>
+      </c>
+      <c r="B105" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C105" s="4" t="n">
+        <v>102</v>
+      </c>
+      <c r="D105" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="E105" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="F105" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="G105" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="H105" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I105" s="13" t="n">
+        <v>800</v>
+      </c>
+      <c r="J105" s="14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K105" s="5" t="n">
+        <v>400</v>
+      </c>
+      <c r="L105" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="M105" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N105" s="5" t="n">
+        <f aca="false">K105*M105</f>
+        <v>0</v>
+      </c>
+      <c r="O105" s="15" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A106" s="4" t="n">
+        <v>1769</v>
+      </c>
+      <c r="B106" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C106" s="4" t="n">
+        <v>103</v>
+      </c>
+      <c r="D106" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="E106" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="F106" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="G106" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="H106" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I106" s="13" t="n">
+        <v>265</v>
+      </c>
+      <c r="J106" s="14" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="K106" s="5" t="n">
+        <v>145.75</v>
+      </c>
+      <c r="L106" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="M106" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N106" s="5" t="n">
+        <f aca="false">K106*M106</f>
+        <v>0</v>
+      </c>
+      <c r="O106" s="15" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A107" s="4" t="n">
+        <v>1769</v>
+      </c>
+      <c r="B107" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C107" s="4" t="n">
+        <v>104</v>
+      </c>
+      <c r="D107" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="E107" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="F107" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="G107" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="H107" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I107" s="13" t="n">
+        <v>300</v>
+      </c>
+      <c r="J107" s="14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K107" s="5" t="n">
+        <v>150</v>
+      </c>
+      <c r="L107" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="M107" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N107" s="5" t="n">
+        <f aca="false">K107*M107</f>
+        <v>0</v>
+      </c>
+      <c r="O107" s="15" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A108" s="4" t="n">
+        <v>1769</v>
+      </c>
+      <c r="B108" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C108" s="4" t="n">
+        <v>105</v>
+      </c>
+      <c r="D108" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="E108" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="F108" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="G108" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="H108" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I108" s="13" t="n">
+        <v>700</v>
+      </c>
+      <c r="J108" s="14" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K108" s="5" t="n">
+        <v>420</v>
+      </c>
+      <c r="L108" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="M108" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N108" s="5" t="n">
+        <f aca="false">K108*M108</f>
+        <v>0</v>
+      </c>
+      <c r="O108" s="15" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A109" s="4" t="n">
+        <v>1769</v>
+      </c>
+      <c r="B109" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C109" s="4" t="n">
+        <v>106</v>
+      </c>
+      <c r="D109" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="E109" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="F109" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="G109" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="H109" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I109" s="13" t="n">
+        <v>800</v>
+      </c>
+      <c r="J109" s="14" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="K109" s="5" t="n">
+        <v>440</v>
+      </c>
+      <c r="L109" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="M109" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="N109" s="5" t="n">
+        <f aca="false">K109*M109</f>
+        <v>5280</v>
+      </c>
+      <c r="O109" s="16" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A110" s="4" t="n">
+        <v>1769</v>
+      </c>
+      <c r="B110" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C110" s="4" t="n">
+        <v>107</v>
+      </c>
+      <c r="D110" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="E110" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="F110" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="G110" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="H110" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I110" s="13" t="n">
+        <v>265</v>
+      </c>
+      <c r="J110" s="14" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="K110" s="5" t="n">
+        <v>145.75</v>
+      </c>
+      <c r="L110" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="M110" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N110" s="5" t="n">
+        <f aca="false">K110*M110</f>
+        <v>0</v>
+      </c>
+      <c r="O110" s="15" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A111" s="4" t="n">
+        <v>1769</v>
+      </c>
+      <c r="B111" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C111" s="4" t="n">
+        <v>108</v>
+      </c>
+      <c r="D111" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="E111" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="F111" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="G111" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="H111" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I111" s="13" t="n">
+        <v>200</v>
+      </c>
+      <c r="J111" s="14" t="n">
+        <v>0.0425</v>
+      </c>
+      <c r="K111" s="5" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="L111" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="M111" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N111" s="5" t="n">
+        <f aca="false">K111*M111</f>
+        <v>8.5</v>
+      </c>
+      <c r="O111" s="15"/>
+    </row>
+    <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A112" s="4" t="n">
+        <v>1769</v>
+      </c>
+      <c r="B112" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C112" s="4" t="n">
+        <v>109</v>
+      </c>
+      <c r="D112" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="E112" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="F112" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="G112" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="H112" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I112" s="13" t="n">
+        <v>100</v>
+      </c>
+      <c r="J112" s="14" t="n">
+        <v>0.0875</v>
+      </c>
+      <c r="K112" s="5" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="L112" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="M112" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N112" s="5" t="n">
+        <f aca="false">K112*M112</f>
+        <v>8.75</v>
+      </c>
+      <c r="O112" s="15"/>
     </row>
   </sheetData>
-  <autoFilter ref="A3:O104"/>
+  <autoFilter ref="A3:O112"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>

--- a/コミッション報告_2026年10月/朴G/コミッション明細_2026年10月_朴G_まとめ.xlsx
+++ b/コミッション報告_2026年10月/朴G/コミッション明細_2026年10月_朴G_まとめ.xlsx
@@ -12,7 +12,7 @@
     <sheet name="明細" sheetId="2" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">明細!$A$3:$O$112</definedName>
+    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">明細!$A$3:$O$113</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="798" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="807" uniqueCount="152">
   <si>
     <r>
       <rPr>
@@ -887,6 +887,52 @@
   </si>
   <si>
     <t xml:space="preserve">Yuki Takaoka</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">契約</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年目のため平準（毎月お支払い）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ライダー</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -1421,11 +1467,11 @@
         <v>7</v>
       </c>
       <c r="C4" s="4" t="n">
-        <f aca="false">COUNTIF(明細!$A$4:$A$112,A4)</f>
+        <f aca="false">COUNTIF(明細!$A$4:$A$113,A4)</f>
         <v>52</v>
       </c>
       <c r="D4" s="5" t="n">
-        <f aca="false">SUMIF(明細!$A$4:$A$112,A4,明細!$N$4:$N$112)</f>
+        <f aca="false">SUMIF(明細!$A$4:$A$113,A4,明細!$N$4:$N$113)</f>
         <v>23442</v>
       </c>
       <c r="E4" s="5" t="n">
@@ -1444,11 +1490,11 @@
         <v>8</v>
       </c>
       <c r="C5" s="4" t="n">
-        <f aca="false">COUNTIF(明細!$A$4:$A$112,A5)</f>
+        <f aca="false">COUNTIF(明細!$A$4:$A$113,A5)</f>
         <v>3</v>
       </c>
       <c r="D5" s="5" t="n">
-        <f aca="false">SUMIF(明細!$A$4:$A$112,A5,明細!$N$4:$N$112)</f>
+        <f aca="false">SUMIF(明細!$A$4:$A$113,A5,明細!$N$4:$N$113)</f>
         <v>1260</v>
       </c>
       <c r="E5" s="5" t="n">
@@ -1467,11 +1513,11 @@
         <v>9</v>
       </c>
       <c r="C6" s="4" t="n">
-        <f aca="false">COUNTIF(明細!$A$4:$A$112,A6)</f>
+        <f aca="false">COUNTIF(明細!$A$4:$A$113,A6)</f>
         <v>2</v>
       </c>
       <c r="D6" s="5" t="n">
-        <f aca="false">SUMIF(明細!$A$4:$A$112,A6,明細!$N$4:$N$112)</f>
+        <f aca="false">SUMIF(明細!$A$4:$A$113,A6,明細!$N$4:$N$113)</f>
         <v>960</v>
       </c>
       <c r="E6" s="5" t="n">
@@ -1490,11 +1536,11 @@
         <v>10</v>
       </c>
       <c r="C7" s="4" t="n">
-        <f aca="false">COUNTIF(明細!$A$4:$A$112,A7)</f>
+        <f aca="false">COUNTIF(明細!$A$4:$A$113,A7)</f>
         <v>1</v>
       </c>
       <c r="D7" s="5" t="n">
-        <f aca="false">SUMIF(明細!$A$4:$A$112,A7,明細!$N$4:$N$112)</f>
+        <f aca="false">SUMIF(明細!$A$4:$A$113,A7,明細!$N$4:$N$113)</f>
         <v>1260</v>
       </c>
       <c r="E7" s="5" t="n">
@@ -1513,11 +1559,11 @@
         <v>11</v>
       </c>
       <c r="C8" s="4" t="n">
-        <f aca="false">COUNTIF(明細!$A$4:$A$112,A8)</f>
+        <f aca="false">COUNTIF(明細!$A$4:$A$113,A8)</f>
         <v>2</v>
       </c>
       <c r="D8" s="5" t="n">
-        <f aca="false">SUMIF(明細!$A$4:$A$112,A8,明細!$N$4:$N$112)</f>
+        <f aca="false">SUMIF(明細!$A$4:$A$113,A8,明細!$N$4:$N$113)</f>
         <v>810</v>
       </c>
       <c r="E8" s="5" t="n">
@@ -1536,11 +1582,11 @@
         <v>12</v>
       </c>
       <c r="C9" s="4" t="n">
-        <f aca="false">COUNTIF(明細!$A$4:$A$112,A9)</f>
+        <f aca="false">COUNTIF(明細!$A$4:$A$113,A9)</f>
         <v>2</v>
       </c>
       <c r="D9" s="5" t="n">
-        <f aca="false">SUMIF(明細!$A$4:$A$112,A9,明細!$N$4:$N$112)</f>
+        <f aca="false">SUMIF(明細!$A$4:$A$113,A9,明細!$N$4:$N$113)</f>
         <v>4224</v>
       </c>
       <c r="E9" s="5" t="n">
@@ -1559,11 +1605,11 @@
         <v>13</v>
       </c>
       <c r="C10" s="4" t="n">
-        <f aca="false">COUNTIF(明細!$A$4:$A$112,A10)</f>
+        <f aca="false">COUNTIF(明細!$A$4:$A$113,A10)</f>
         <v>5</v>
       </c>
       <c r="D10" s="5" t="n">
-        <f aca="false">SUMIF(明細!$A$4:$A$112,A10,明細!$N$4:$N$112)</f>
+        <f aca="false">SUMIF(明細!$A$4:$A$113,A10,明細!$N$4:$N$113)</f>
         <v>2100</v>
       </c>
       <c r="E10" s="5" t="n">
@@ -1582,11 +1628,11 @@
         <v>14</v>
       </c>
       <c r="C11" s="4" t="n">
-        <f aca="false">COUNTIF(明細!$A$4:$A$112,A11)</f>
+        <f aca="false">COUNTIF(明細!$A$4:$A$113,A11)</f>
         <v>10</v>
       </c>
       <c r="D11" s="5" t="n">
-        <f aca="false">SUMIF(明細!$A$4:$A$112,A11,明細!$N$4:$N$112)</f>
+        <f aca="false">SUMIF(明細!$A$4:$A$113,A11,明細!$N$4:$N$113)</f>
         <v>3384</v>
       </c>
       <c r="E11" s="5" t="n">
@@ -1605,11 +1651,11 @@
         <v>15</v>
       </c>
       <c r="C12" s="4" t="n">
-        <f aca="false">COUNTIF(明細!$A$4:$A$112,A12)</f>
+        <f aca="false">COUNTIF(明細!$A$4:$A$113,A12)</f>
         <v>13</v>
       </c>
       <c r="D12" s="5" t="n">
-        <f aca="false">SUMIF(明細!$A$4:$A$112,A12,明細!$N$4:$N$112)</f>
+        <f aca="false">SUMIF(明細!$A$4:$A$113,A12,明細!$N$4:$N$113)</f>
         <v>16806</v>
       </c>
       <c r="E12" s="5" t="n">
@@ -1628,11 +1674,11 @@
         <v>16</v>
       </c>
       <c r="C13" s="4" t="n">
-        <f aca="false">COUNTIF(明細!$A$4:$A$112,A13)</f>
+        <f aca="false">COUNTIF(明細!$A$4:$A$113,A13)</f>
         <v>7</v>
       </c>
       <c r="D13" s="5" t="n">
-        <f aca="false">SUMIF(明細!$A$4:$A$112,A13,明細!$N$4:$N$112)</f>
+        <f aca="false">SUMIF(明細!$A$4:$A$113,A13,明細!$N$4:$N$113)</f>
         <v>1200</v>
       </c>
       <c r="E13" s="5" t="n">
@@ -1651,11 +1697,11 @@
         <v>17</v>
       </c>
       <c r="C14" s="4" t="n">
-        <f aca="false">COUNTIF(明細!$A$4:$A$112,A14)</f>
+        <f aca="false">COUNTIF(明細!$A$4:$A$113,A14)</f>
         <v>4</v>
       </c>
       <c r="D14" s="5" t="n">
-        <f aca="false">SUMIF(明細!$A$4:$A$112,A14,明細!$N$4:$N$112)</f>
+        <f aca="false">SUMIF(明細!$A$4:$A$113,A14,明細!$N$4:$N$113)</f>
         <v>1080</v>
       </c>
       <c r="E14" s="5" t="n">
@@ -1674,11 +1720,11 @@
         <v>18</v>
       </c>
       <c r="C15" s="4" t="n">
-        <f aca="false">COUNTIF(明細!$A$4:$A$112,A15)</f>
-        <v>8</v>
+        <f aca="false">COUNTIF(明細!$A$4:$A$113,A15)</f>
+        <v>9</v>
       </c>
       <c r="D15" s="5" t="n">
-        <f aca="false">SUMIF(明細!$A$4:$A$112,A15,明細!$N$4:$N$112)</f>
+        <f aca="false">SUMIF(明細!$A$4:$A$113,A15,明細!$N$4:$N$113)</f>
         <v>5297.25</v>
       </c>
       <c r="E15" s="5" t="n">
@@ -1695,7 +1741,7 @@
       </c>
       <c r="C16" s="7" t="n">
         <f aca="false">SUM(C4:C15)</f>
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D16" s="8" t="n">
         <f aca="false">SUM(D4:D15)</f>
@@ -1731,7 +1777,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:O112"/>
+  <dimension ref="A1:O113"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
@@ -6983,7 +7029,9 @@
         <f aca="false">K111*M111</f>
         <v>8.5</v>
       </c>
-      <c r="O111" s="15"/>
+      <c r="O111" s="16" t="s">
+        <v>150</v>
+      </c>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="4" t="n">
@@ -7029,10 +7077,60 @@
         <f aca="false">K112*M112</f>
         <v>8.75</v>
       </c>
-      <c r="O112" s="15"/>
+      <c r="O112" s="16" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A113" s="4" t="n">
+        <v>1769</v>
+      </c>
+      <c r="B113" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C113" s="4" t="n">
+        <v>110</v>
+      </c>
+      <c r="D113" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="E113" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="F113" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="G113" s="12" t="s">
+        <v>151</v>
+      </c>
+      <c r="H113" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I113" s="13" t="n">
+        <v>300</v>
+      </c>
+      <c r="J113" s="14" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K113" s="5" t="n">
+        <v>180</v>
+      </c>
+      <c r="L113" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="M113" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N113" s="5" t="n">
+        <f aca="false">K113*M113</f>
+        <v>0</v>
+      </c>
+      <c r="O113" s="15" t="s">
+        <v>43</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:O112"/>
+  <autoFilter ref="A3:O113"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
